--- a/daily_matches/job_matches_2026-06-09.xlsx
+++ b/daily_matches/job_matches_2026-06-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, MLflow, Kubernetes, Apache Airflow, CI/CD, Jenkins, Terraform, Git</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Azure ML</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e2b721d35d7a5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e5abed50f2367d51</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Software Engineer III - Data Platform</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, CI/CD, Git, Databricks, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d18ea85c2c928c35</t>
+          <t>https://www.indeed.com/viewjob?jk=257ec7c1915b24c6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist Senior</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>21.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, TensorFlow, PyTorch, Keras, Docker, CI/CD, Git, PySpark</t>
+          <t>RAG, Prompt Engineering, XGBoost, S3, Data Lake, AKS, Apache Airflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d52c7a1e79e579</t>
+          <t>https://www.indeed.com/viewjob?jk=76c7190df188f528</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior AI Operations Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ScandyCandy LLC</t>
+          <t>Claritev</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>21.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, XGBoost, Git, Databricks, Kafka, Tableau, Power BI, Quicksight</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Mistral, MLflow, Docker, Kubernetes, AKS, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc118ef6518ab44c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1103c64558f430</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Full Stack Engineer</t>
+          <t>Senior Engineer, AI/ML Software</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, S3, Docker, Kubernetes, CI/CD, Git, MySQL, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, PyTorch, XGBoost, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c4b06a84a76fe1</t>
+          <t>https://www.indeed.com/viewjob?jk=664a13900407cad4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Snooze an AM Eatery</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, Data Lake, FastAPI, Apache Airflow, Snowflake, Python, SQL, R</t>
+          <t>RAG, Copilot, BigQuery, FastAPI, Docker, CI/CD, GitHub Actions, Git, BigQuery, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65eaed35b3d68901</t>
+          <t>https://www.indeed.com/viewjob?jk=947710ea68d4354a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>AI/ML Engineer - RecSys (ML Ops)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Data Surge</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, CI/CD, Databricks, MySQL, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, AWS SageMaker, Azure ML, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afc90802a9cd7a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=34cf51cb87306bf3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist - Career</t>
+          <t>Senior Engineer 2: AI Agentic Platform (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, Snowflake, Hadoop, Dask, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, Redshift, BigQuery, Docker, Kubernetes, CI/CD, Git, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131163ee107dda55</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a42d221dac8991</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Atlas Air, Inc.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Redford, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Databricks, BigQuery, Redshift, Python, SQL, R, Java, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, XGBoost, LightGBM, BigQuery, Dataflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64f1dac382245c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=c29332168c78c58c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior Software Engineer, BTH Engineering</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Atlas Air, Inc.</t>
+          <t>BULLISH GLOBAL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Databricks, BigQuery, Redshift, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, BigQuery, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b09bf18afcef2fd</t>
+          <t>https://www.indeed.com/viewjob?jk=51b375a6f9ba623a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Machine Learning Engineer, Co-op</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Atlas Air, Inc.</t>
+          <t>Ancestry</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Erlanger, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Databricks, BigQuery, Redshift, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=201c6fed5275fa87</t>
+          <t>https://www.indeed.com/viewjob?jk=9bbf90be806bb359</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rise Collective</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S3, EC2, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3b252b91a197e5</t>
+          <t>https://www.indeed.com/viewjob?jk=4e32c70852b2e7e9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
+          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ead8343cec4879</t>
+          <t>https://www.indeed.com/viewjob?jk=3f53654a42d5f44e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
+          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=162c2ab9f292809c</t>
+          <t>https://www.indeed.com/viewjob?jk=74408bc2ca90f29e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
+          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7be54a20fbf4431</t>
+          <t>https://www.indeed.com/viewjob?jk=cfcd3234ed7c76b1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer - Education</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, MLflow, CI/CD, Terraform, Git, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329729d038697e60</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5d60890bd05332</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ML / AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Gradient</t>
+          <t>Crumbl Cookies Franchises</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, FAISS, Pinecone, TensorFlow, PyTorch, OpenCV, Docker, Python, R, Scala</t>
+          <t>Data Scientist, RAG, S3, Glue, Terraform, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=197ca293349620f6</t>
+          <t>https://www.indeed.com/viewjob?jk=60db0ac4d21d1076</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>DTN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,102 +1091,102 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef437e0f2fd6acc</t>
+          <t>https://www.indeed.com/viewjob?jk=cb35c7b57058adb4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Crumbl Cookies Franchises</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, Git, Databricks, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, S3, Glue, Terraform, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3937c8d4c968d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c53bb7a7aa686c9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Rapid Eagle Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d135475bf2adc12</t>
+          <t>https://www.indeed.com/viewjob?jk=04eb778a23284ca5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Commercial Data &amp; Insights Analyst - Bracco Diagnostics Inc.</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bracco Medical Technologies</t>
+          <t>ASRC Federal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Git, Tableau, Power BI, Matplotlib, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3f418a9e24cbabf</t>
+          <t>https://www.indeed.com/viewjob?jk=a425470df97320db</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Analyst - IC 2</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bed Bath &amp; Beyond</t>
+          <t>Proofpoint</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BigQuery, BigQuery, Tableau, Power BI, MicroStrategy, Python, SQL, R, Optimization, Hypothesis Testing</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, Git, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8eb9f7d0706404</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d96369082f1880</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer, Embedded Agentic AI</t>
+          <t>Sr Software Engineer- Java full stack</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, TensorFlow, PyTorch, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, MongoDB, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,42 +1266,637 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b23267569085393d</t>
+          <t>https://www.indeed.com/viewjob?jk=46b735abc0b2aacc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Audio Intelligence</t>
+          <t>Intelligent Automation Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vivint</t>
+          <t>City of Hope</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Cortex, Snowflake, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16b49fe6e0399a27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Intregrations Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Trucordia</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Lindon, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, Docker, CI/CD, Git, Snowflake, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=500ed1260d8579e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Agentic Software Test Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Trane Technologies</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>La Crosse, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64727dfb64f4c1ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=debc73a0a4d41c46</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Wayfair Sponsored Shops</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Wayfair</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Kafka, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1700b3ad8a2acabe</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Spurs Sports &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, NoSQL, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31a3c71dc92d0e0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CD&amp;A Data Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Viasat</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Carlsbad, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>BigQuery, Terraform, Git, BigQuery, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6cb0aa04ee83dc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Beacon Talent</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Docker, Git, Snowflake, Redshift, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56e3a8ed889688f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Jenkins, Terraform, Git, Databricks, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d23e98febb4af71d</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Chickasaw Nation Industries</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce9889ce51319f1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Cloud Infrastructure Engineer (Copy)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HELIX</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad1d142614f8df0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Technical Support Engineer (Statsig)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Amplitude</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>10</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f342424d6fb306d</t>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Git, Snowflake, BigQuery, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8471f48167c3c741</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Technical Support Engineer (Statsig)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Amplitude</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>West New York, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Git, Snowflake, BigQuery, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=253083b0a12701b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Threat Detection &amp; Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Berkeley Heights, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, CI/CD, Terraform, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae05eb013057f83f</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Technical Support Engineer (Statsig)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Amplitude</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Git, Snowflake, BigQuery, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3007e1af60c6576</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Product</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ThredUp</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Python, SQL, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1210b135622200d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Data Science Analyst</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Itron</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Liberty Lake, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4449c9167261c893</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Analyst, Commercial Analytics &amp; Data Science</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>adswizz</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, XGBoost, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2fa094ee1d1f166</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-09.xlsx
+++ b/daily_matches/job_matches_2026-06-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>AI Solution Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HealthStream</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, S3</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6929e10d2183d6c</t>
+          <t>https://www.indeed.com/viewjob?jk=f647259c84954990</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer (Requiring GCP)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Synapse, Data Lake, CI/CD, Terraform, Snowflake, Databricks, Redshift, PySpark</t>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30d85c0bd52ccea6</t>
+          <t>https://www.indeed.com/viewjob?jk=a9cfe57c8aa77945</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior Data Engineer (Requiring GCP)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Atlas Air, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Databricks, BigQuery, Redshift, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4e82faffdc08ac9</t>
+          <t>https://www.indeed.com/viewjob?jk=546ae471f5ede086</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Production Digitalization Intern (Fall 2026)</t>
+          <t>Senior Data Engineer (Requiring GCP)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BMW Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Woodruff, SC, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Glue, Athena, CI/CD, Git, PostgreSQL, Quicksight, Python, SQL, R</t>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,392 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2c3fbbbf2753ab</t>
+          <t>https://www.indeed.com/viewjob?jk=1c811d03d5aca192</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer, Embedded Agentic AI</t>
+          <t>Senior Data Engineer (Requiring GCP)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b6a62dfef2d6dab</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Requiring GCP)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8656393b23155db</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Azure Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Carollo Engineers, Inc.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab80492ce8c08674</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sr. Engineer, Site Reliability</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Syniti</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, S3, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a9aaaa695359595</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer II</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kirkland &amp; Ellis</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=513537d5ace7d85f</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer II</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kirkland &amp; Ellis</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8700ec14a3173f7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>WA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36646cede260b3e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Full Stack AI Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>mLabs</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, FastAPI, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ed859f9cfbd2209</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CD&amp;A Data Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Viasat</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Carlsbad, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BigQuery, Terraform, Git, BigQuery, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54bc52360158a211</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Decision Science Analyst II - Customer Data</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HEB</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, PySpark, Tableau, MicroStrategy, Python, SQL, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=800bdbb3b68535d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Analyst, Commercial Analytics &amp; Data Science</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SiriusXM</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, TensorFlow, PyTorch, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, XGBoost, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a66c6c49bec438</t>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b15702e2ad3d343b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-09.xlsx
+++ b/daily_matches/job_matches_2026-06-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Solution Engineer</t>
+          <t>AI Engineer - AI/ML</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, TensorFlow, Data Lake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f647259c84954990</t>
+          <t>https://www.indeed.com/viewjob?jk=603c741187a35795</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Requiring GCP)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9cfe57c8aa77945</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1214688100a67a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Requiring GCP)</t>
+          <t>Distinguished Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, Kubernetes, CI/CD, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=546ae471f5ede086</t>
+          <t>https://www.indeed.com/viewjob?jk=491a7be916eb7485</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Requiring GCP)</t>
+          <t>Distinguished Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, Kubernetes, CI/CD, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c811d03d5aca192</t>
+          <t>https://www.indeed.com/viewjob?jk=87547326060f6310</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Requiring GCP)</t>
+          <t>Distinguished Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, Kubernetes, CI/CD, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6a62dfef2d6dab</t>
+          <t>https://www.indeed.com/viewjob?jk=efc36f0f520e61ce</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Requiring GCP)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+          <t>Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,54 +671,54 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8656393b23155db</t>
+          <t>https://www.indeed.com/viewjob?jk=34801161eca101a2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Carollo Engineers, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Snowflake, Databricks, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab80492ce8c08674</t>
+          <t>https://www.indeed.com/viewjob?jk=9652a3e159336480</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Site Reliability</t>
+          <t>Full-Stack Software Engineer – Vehicle Software Engineering Services</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Syniti</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,73 +727,73 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Gemini, S3, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9aaaa695359595</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e3f3d87b0c456d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer II</t>
+          <t>Associate Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=513537d5ace7d85f</t>
+          <t>https://www.indeed.com/viewjob?jk=f990189dc2794b76</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer II</t>
+          <t>Senior AI Product Engineer | Growth and Transformation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8700ec14a3173f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=8d1014e474f6d7fa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Cypress, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, Kafka, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36646cede260b3e6</t>
+          <t>https://www.indeed.com/viewjob?jk=be2ef33d0192f63d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Senior AI ML Engineer - Remote</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>mLabs</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, FastAPI, Git, Python, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ed859f9cfbd2209</t>
+          <t>https://www.indeed.com/viewjob?jk=597ba90f094013d1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CD&amp;A Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BigQuery, Terraform, Git, BigQuery, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,77 +916,357 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54bc52360158a211</t>
+          <t>https://www.indeed.com/viewjob?jk=e86ae3c2b2b74b36</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Decision Science Analyst II - Customer Data</t>
+          <t>Junior AI Engineer - Computer Vision</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HEB</t>
+          <t>InnovationTeam</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Databricks, PySpark, Tableau, MicroStrategy, Python, SQL, R, Optimization, A/B Testing</t>
+          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, OpenCV, YOLO, Docker, Python, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=800bdbb3b68535d3</t>
+          <t>https://www.indeed.com/viewjob?jk=e6459c227f59ac98</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analyst, Commercial Analytics &amp; Data Science</t>
+          <t>AI Product Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SiriusXM</t>
+          <t>KORE Power</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Pinecone, Docker, Kubernetes, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ae111d8a377abf8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Bricks Migration and Support engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f89526bd8706b6bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Full Stack Java/React) - Commissions Platform - HYBRID</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=045379d7ae411e5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, Git, MongoDB, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f2b4c048211ffc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AI Platform Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>New York, NY, US USA</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed4891ffb94b6124</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AI Systems Engineer (In-Person/No remote work)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Keystone Sports Construction</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Phoenixville, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>10</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, XGBoost, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b15702e2ad3d343b</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Prompt Engineering, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1bab2620b66112a</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Development Engineer 3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Hologic</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Marlborough, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c385e444926bb7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Children's National Hospital</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, MLflow, Databricks, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=935ca7237c28a1d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Synapse, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11e0ebb24cd18ba5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-09.xlsx
+++ b/daily_matches/job_matches_2026-06-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer - AI/ML</t>
+          <t>AI Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, TensorFlow, Data Lake</t>
+          <t>RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, OpenCV, YOLO, AWS SageMaker, GCP Vertex AI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603c741187a35795</t>
+          <t>https://www.indeed.com/viewjob?jk=212d73dd2934b416</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - GTM Team</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, LangChain, XGBoost, FastAPI, Docker, Kubernetes, AKS, CI/CD, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1214688100a67a</t>
+          <t>https://www.indeed.com/viewjob?jk=71238d288bcde281</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Distinguished Machine Learning Engineer</t>
+          <t>Data Engineer - GTM Team</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, Kubernetes, CI/CD, Snowflake</t>
+          <t>Data Scientist, LangChain, XGBoost, FastAPI, Docker, Kubernetes, AKS, CI/CD, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491a7be916eb7485</t>
+          <t>https://www.indeed.com/viewjob?jk=97105581153651c2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Distinguished Machine Learning Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, Kubernetes, CI/CD, Snowflake</t>
+          <t>Data Scientist, RAG, S3, Data Lake, Kinesis, Docker, Kubernetes, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87547326060f6310</t>
+          <t>https://www.indeed.com/viewjob?jk=ae38a9c283b62879</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Distinguished Machine Learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Verana Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, Kubernetes, CI/CD, Snowflake</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,49 +636,49 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efc36f0f520e61ce</t>
+          <t>https://www.indeed.com/viewjob?jk=b898217d67c6bb05</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34801161eca101a2</t>
+          <t>https://www.indeed.com/viewjob?jk=260e9231f9bc608e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Snowflake, Databricks, Kafka, NoSQL</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9652a3e159336480</t>
+          <t>https://www.indeed.com/viewjob?jk=4490cabd1816492f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer – Vehicle Software Engineering Services</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>ReadyOn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, LightGBM, CatBoost, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e3f3d87b0c456d</t>
+          <t>https://www.indeed.com/viewjob?jk=f34570c1dc5ff7b4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate Site Reliability Engineer</t>
+          <t>Data Scientist III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>OpenX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, BigQuery, Dataflow, Git, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f990189dc2794b76</t>
+          <t>https://www.indeed.com/viewjob?jk=00ed9e2dab69eec4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Product Engineer | Growth and Transformation</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, Databricks, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d1014e474f6d7fa</t>
+          <t>https://www.indeed.com/viewjob?jk=8e55aae80dce9806</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cypress, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
+          <t>RAG, Copilot, S3, CI/CD, GitHub Actions, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be2ef33d0192f63d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa97fcdc7f844184</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI ML Engineer - Remote</t>
+          <t>Sr Strategic Data Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Healthfirst</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Glue, Redshift, Kinesis, Redshift, Hadoop, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597ba90f094013d1</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2e59ee35daead0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Forward Deployed Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Rackspace Technology</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e86ae3c2b2b74b36</t>
+          <t>https://www.indeed.com/viewjob?jk=4b6d03269c072a41</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Junior AI Engineer - Computer Vision</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>InnovationTeam</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, OpenCV, YOLO, Docker, Python, R, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, Keras, PySpark, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6459c227f59ac98</t>
+          <t>https://www.indeed.com/viewjob?jk=b7d7cd30a461b791</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KORE Power</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Docker, Kubernetes, Kafka, Python, SQL, R, Scala</t>
+          <t>RAG, BigQuery, Kubernetes, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ae111d8a377abf8</t>
+          <t>https://www.indeed.com/viewjob?jk=2f3ea43169f28b5a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Bricks Migration and Support engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Prompt Engineering, MLflow, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f89526bd8706b6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9184a594a80c4316</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Java/React) - Commissions Platform - HYBRID</t>
+          <t>Advisor, Data Science</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, LangChain, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=045379d7ae411e5c</t>
+          <t>https://www.indeed.com/viewjob?jk=2368d501bcbb0504</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Support Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Symbotic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,29 +1081,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Git, MongoDB, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f2b4c048211ffc6</t>
+          <t>https://www.indeed.com/viewjob?jk=4c8227172942df9b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Platform Infrastructure Engineer</t>
+          <t>AWS Serverless Full Stack Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1112,11 +1112,11 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Generative AI, RAG, S3, Glue, Quicksight, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4891ffb94b6124</t>
+          <t>https://www.indeed.com/viewjob?jk=38feb710a36ff9f4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Systems Engineer (In-Person/No remote work)</t>
+          <t>Technical Support Engineer (Openstack, Kubernetes)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Keystone Sports Construction</t>
+          <t>Mirantis</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phoenixville, PA, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, PostgreSQL, MySQL, Cassandra, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1bab2620b66112a</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf06c0aae2a3fba</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Development Engineer 3</t>
+          <t>Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hologic</t>
+          <t>VSG Business Solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Scala</t>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c385e444926bb7e</t>
+          <t>https://www.indeed.com/viewjob?jk=affe8303aaf58004</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Support Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Children's National Hospital</t>
+          <t>Symbotic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, Databricks, NoSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=935ca7237c28a1d5</t>
+          <t>https://www.indeed.com/viewjob?jk=8d18dd6c2082b5ee</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>Product Data Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tripadvisor</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Synapse, Git, Snowflake, Databricks, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Tableau, Python, SQL, R, Scala, Bayesian, A/B Testing</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,77 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11e0ebb24cd18ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=641894f7c708f46c</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Divisions Maintenance Group</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Git, Python, SQL, R, Optimization, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ff82f9b4224b92d</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Divisions Maintenance Group</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Git, Python, SQL, R, Optimization, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=acb0bd7ade2e6977</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-09.xlsx
+++ b/daily_matches/job_matches_2026-06-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Software Engineer, Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, OpenCV, YOLO, AWS SageMaker, GCP Vertex AI</t>
+          <t>Data Scientist, Redshift, BigQuery, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212d73dd2934b416</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c144461aa2d176</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer - GTM Team</t>
+          <t>Solutions Architect, Customer Success - US (Remote)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, XGBoost, FastAPI, Docker, Kubernetes, AKS, CI/CD, Snowflake, Databricks</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, S3, BigQuery, Kinesis, MLflow, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71238d288bcde281</t>
+          <t>https://www.indeed.com/viewjob?jk=5e29186d332dfa69</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer - GTM Team</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>PineCone</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, XGBoost, FastAPI, Docker, Kubernetes, AKS, CI/CD, Snowflake, Databricks</t>
+          <t>RAG, Pinecone, Redshift, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97105581153651c2</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6aa5155c88f566</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Senior Data Engineer (AWS, Databricks)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Data Lake, Kinesis, Docker, Kubernetes, Terraform, Git, Databricks</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae38a9c283b62879</t>
+          <t>https://www.indeed.com/viewjob?jk=74c4df1b9aa839f0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Service Delivery Center, AI &amp; Data - Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Verana Health</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL, Python, SQL</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, Docker, Kubernetes, AKS, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b898217d67c6bb05</t>
+          <t>https://www.indeed.com/viewjob?jk=402e886cef74b630</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data/Machine Learning Engineer</t>
+          <t>Customer Data Platform Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python, SQL</t>
+          <t>RAG, S3, Glue, Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=260e9231f9bc608e</t>
+          <t>https://www.indeed.com/viewjob?jk=a6303a5693fb08b9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer (Max $75/hr W2)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Lenmar Consulting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+          <t>Copilot, Athena, Redshift, Git, Snowflake, Databricks, Redshift, Tableau, Quicksight, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4490cabd1816492f</t>
+          <t>https://www.indeed.com/viewjob?jk=163ae6cc8be39c56</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ReadyOn</t>
+          <t>SportsBiz Group Inc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, LightGBM, CatBoost, CI/CD, Python, SQL</t>
+          <t>AI Engineer, Copilot, S3, Data Lake, Docker, Kubernetes, CI/CD, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34570c1dc5ff7b4</t>
+          <t>https://www.indeed.com/viewjob?jk=eecd0ded4500842f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist III</t>
+          <t>Full Stack AI Product Engineer (DataEdge)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OpenX</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, BigQuery, Dataflow, Git, BigQuery, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00ed9e2dab69eec4</t>
+          <t>https://www.indeed.com/viewjob?jk=caded7b3c6bfb312</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Full Stack AI Product Engineer (DataEdge)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, Databricks, BigQuery, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e55aae80dce9806</t>
+          <t>https://www.indeed.com/viewjob?jk=b469cfbb95e6de2a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack AI Product Engineer (DataEdge)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, GitHub Actions, Git, Python, SQL, R, Java</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa97fcdc7f844184</t>
+          <t>https://www.indeed.com/viewjob?jk=35ffec2079d73b49</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Strategic Data Analyst</t>
+          <t>Full Stack AI Product Engineer (DataEdge)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Healthfirst</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,64 +871,64 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Glue, Redshift, Kinesis, Redshift, Hadoop, Tableau, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2e59ee35daead0</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd7c29dab24b04e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer II</t>
+          <t>Full Stack AI Product Engineer (DataEdge)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rackspace Technology</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b6d03269c072a41</t>
+          <t>https://www.indeed.com/viewjob?jk=c3c936d966c8b145</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>HCM- Dallas- Associate, Data Analytics and Reporting- 9625494</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -937,11 +937,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, Keras, PySpark, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Data Lake, Git, Snowflake, MongoDB, NoSQL, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7d7cd30a461b791</t>
+          <t>https://www.indeed.com/viewjob?jk=426e1707f879b63b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Data Scientist 35431</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Juncos, PR, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Git, Databricks, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f3ea43169f28b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=f943667deb1065b5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, MLflow, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, LLaMA, Gemini, TensorFlow, PyTorch, XGBoost, Dataflow, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9184a594a80c4316</t>
+          <t>https://www.indeed.com/viewjob?jk=062076e48bfaecc5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Advisor, Data Science</t>
+          <t>Software Development Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Python, SQL, R, Optimization</t>
+          <t>Machine Learning Engineer, RAG, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2368d501bcbb0504</t>
+          <t>https://www.indeed.com/viewjob?jk=77793594531a288d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Support Software Engineer</t>
+          <t>Sr Software Development Engineer - Core Platform Integration</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, SQL, R</t>
+          <t>RAG, Glue, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c8227172942df9b</t>
+          <t>https://www.indeed.com/viewjob?jk=66f1bbfba1ba3212</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS Serverless Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>NCR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Glue, Quicksight, Python, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38feb710a36ff9f4</t>
+          <t>https://www.indeed.com/viewjob?jk=d8cc9d3e919490ad</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Technical Support Engineer (Openstack, Kubernetes)</t>
+          <t>AI Engineer/Sr Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mirantis</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, PostgreSQL, MySQL, Cassandra, Python, SQL, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Prompt Engineering, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf06c0aae2a3fba</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd4a7ba269953df</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Network Engineer</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VSG Business Solutions</t>
+          <t>DIVERGENT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, PyTorch, Docker, Kubernetes, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=affe8303aaf58004</t>
+          <t>https://www.indeed.com/viewjob?jk=710354a96a498e7d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Support Engineer</t>
+          <t>Software Engineer, New College Grad - 2026, Austin, TX</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R</t>
+          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d18dd6c2082b5ee</t>
+          <t>https://www.indeed.com/viewjob?jk=6df893dd51352b5d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Product Data Scientist</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tripadvisor</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Tableau, Python, SQL, R, Scala, Bayesian, A/B Testing</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641894f7c708f46c</t>
+          <t>https://www.indeed.com/viewjob?jk=94d725fa9ffeab16</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Divisions Maintenance Group</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Git, Python, SQL, R, Optimization, Hypothesis Testing</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,42 +1301,1302 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ff82f9b4224b92d</t>
+          <t>https://www.indeed.com/viewjob?jk=72f33db012062468</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Divisions Maintenance Group</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd55550535093280</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b17fd8044538b11</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4d00d37fa1a3bc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Associate Data Scientist</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, FastAPI, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5ff0fa3f10da5cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Azure Solution Architecture SME</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>S R International Inc</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Jackson, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85d5f9a234b0f80b</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Medisolv Inc</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Clarksville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Glue, Snowflake, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=535ccfe8a6691562</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Development Engineer I</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bde41fb4227c8c5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Development Engineer I</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ca90ff38cd55b7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Development Engineer I</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df5ecfabcdea7c55</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Development Engineer I</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5577a003e72b265</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Development Engineer I</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2243c04399c66ed1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AI Data Engineer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Signet Jewelers</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Coppell, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Redshift, Redshift, PostgreSQL, Power BI, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c4ea33ca7ce21c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Robotics Systems Software Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DIVERGENT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Torrance, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, OpenCV, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c618569fc6963b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Industrial Robotics Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>DIVERGENT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Torrance, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, OpenCV, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eca24e268c18a7e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Real-Time Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DIVERGENT</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Torrance, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, OpenCV, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e83ca9622604149</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>DevOps Engineer - AWS</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TensorWave</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e410daea1e763a2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Cloud Software Intern, GeForce NOW - Fall 2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>EC2, Docker, Kubernetes, CI/CD, Cassandra, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9311582ae861878</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, MySQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02f8dd2b3eba3cc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Autonomy Engineering Development Specialist</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Mossville, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, S3, EC2, Docker, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d473ef7860322708</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AI Intern</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>TRONOX</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Hamilton, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Hadoop, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1af574cf58db45bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Databricks, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fda9e03abcd1738f</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Analytics Associate</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SEER Interactive</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Git, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd97503e1e7a689a</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Software Engineer II - 20201</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Cox Automotive</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Kinesis, Terraform, Git, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99a0bd01cd5f78a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Merrimack, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
         <v>10</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Docker, Git, Python, SQL, R, Optimization, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=acb0bd7ade2e6977</t>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f558ba1012be4859</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e2d2eff3072a8b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Smithfield, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=762857b1d4254cb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Java) - Parametric</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Git, MongoDB, Cassandra, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a31d40a27297a885</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Sr Software Development Engineer - Distributed Systems</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0528618a8c8979a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>AI Product Engineer, Internal Tools</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PlanetArt</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Calabasas, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, Prompt Engineering, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07d65fe18f924abf</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Cat Digital</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e522a800d7880f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>GRP Solutions</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Texas City, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=611d00118289bf7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Beverly Bar</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f8eec3a4e80be0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Technical Solutions Analyst</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Galco Industrial Electronics</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Madison Heights, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Tableau, Power BI, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=757b1a3166ac1fc4</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer (AI Foundations)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c8914315152bec5</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Platform Support Architect</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>DDN</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Pinecone, Docker, Kubernetes, CI/CD, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8d51cfc329b3bf8</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Data Solution Architect/Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Land O'Lakes</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Gray Summit, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Data Scientist, Data Lake, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99bd7930635a6267</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Data Scientist II - Marketing Automation Performance Analytics</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Expedia Group</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Tableau, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=932000411f3a8840</t>
         </is>
       </c>
     </row>
